--- a/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
+++ b/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Executivo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste CEO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas em Risco (MRR)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmentação de Risco" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados Brutos — Contas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Resumo Executivo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Teste CEO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Contas em Risco (MRR)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Segmentação de Risco" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dados Brutos — Contas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 14/09/2026 14:30</t>
+          <t>Gerado automaticamente em 14/09/2026 16:13</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2052,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Company_187</t>
+          <t>Company_436</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A-7a0d69</t>
+          <t>A-34ea2f</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2082,17 +2082,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Company_436</t>
+          <t>Company_187</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A-34ea2f</t>
+          <t>A-7a0d69</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2202,27 +2202,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Company_264</t>
+          <t>Company_32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A-0baac2</t>
+          <t>A-08e34e</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2232,27 +2232,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Company_32</t>
+          <t>Company_264</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A-08e34e</t>
+          <t>A-0baac2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2292,27 +2292,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Company_96</t>
+          <t>Company_463</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A-8b25f2</t>
+          <t>A-798a3f</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2322,27 +2322,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Company_463</t>
+          <t>Company_96</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A-798a3f</t>
+          <t>A-8b25f2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2472,27 +2472,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Company_110</t>
+          <t>Company_221</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A-425e76</t>
+          <t>A-d922bf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2502,27 +2502,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Company_221</t>
+          <t>Company_110</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A-d922bf</t>
+          <t>A-425e76</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2532,27 +2532,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Company_327</t>
+          <t>Company_55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A-600734</t>
+          <t>A-4c38bc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2562,27 +2562,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Company_55</t>
+          <t>Company_327</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A-4c38bc</t>
+          <t>A-600734</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2772,27 +2772,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Company_439</t>
+          <t>Company_324</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A-b11cd0</t>
+          <t>A-6a7c9d</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2802,27 +2802,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Company_324</t>
+          <t>Company_439</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A-6a7c9d</t>
+          <t>A-b11cd0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3012,17 +3012,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Company_10</t>
+          <t>Company_1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A-592832</t>
+          <t>A-43a9e3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3042,17 +3042,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Company_1</t>
+          <t>Company_10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A-43a9e3</t>
+          <t>A-592832</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3342,27 +3342,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Company_369</t>
+          <t>Company_229</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A-40de06</t>
+          <t>A-4ae22a</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -3372,27 +3372,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Company_229</t>
+          <t>Company_369</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A-4ae22a</t>
+          <t>A-40de06</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3852,27 +3852,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Company_357</t>
+          <t>Company_429</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A-1f559b</t>
+          <t>A-7641d3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3882,27 +3882,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Company_429</t>
+          <t>Company_357</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A-7641d3</t>
+          <t>A-1f559b</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3912,17 +3912,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Company_196</t>
+          <t>Company_59</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A-13466a</t>
+          <t>A-9ee962</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3942,17 +3942,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Company_59</t>
+          <t>Company_196</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A-9ee962</t>
+          <t>A-13466a</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3972,22 +3972,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Company_396</t>
+          <t>Company_280</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A-69b156</t>
+          <t>A-443b7c</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4002,22 +4002,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Company_280</t>
+          <t>Company_396</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A-443b7c</t>
+          <t>A-69b156</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4122,12 +4122,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Company_126</t>
+          <t>Company_149</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A-1ac5e0</t>
+          <t>A-eafc6e</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4152,27 +4152,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Company_144</t>
+          <t>Company_427</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A-3932db</t>
+          <t>A-1d5444</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4182,27 +4182,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Company_79</t>
+          <t>Company_126</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A-9208f0</t>
+          <t>A-1ac5e0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -4212,27 +4212,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Company_269</t>
+          <t>Company_8</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A-b07346</t>
+          <t>A-7dacce</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4242,17 +4242,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Company_149</t>
+          <t>Company_79</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A-eafc6e</t>
+          <t>A-9208f0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4272,17 +4272,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Company_117</t>
+          <t>Company_292</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A-95b24a</t>
+          <t>A-b07b56</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4302,27 +4302,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Company_292</t>
+          <t>Company_256</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A-b07b56</t>
+          <t>A-3ce5b8</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4332,27 +4332,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Company_8</t>
+          <t>Company_269</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A-7dacce</t>
+          <t>A-b07346</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4362,27 +4362,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Company_421</t>
+          <t>Company_417</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A-d535f6</t>
+          <t>A-659280</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4392,27 +4392,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Company_417</t>
+          <t>Company_421</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A-659280</t>
+          <t>A-d535f6</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4422,12 +4422,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Company_256</t>
+          <t>Company_103</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A-3ce5b8</t>
+          <t>A-69fad4</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4452,27 +4452,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Company_103</t>
+          <t>Company_144</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A-69fad4</t>
+          <t>A-3932db</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -4482,27 +4482,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Company_427</t>
+          <t>Company_117</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A-1d5444</t>
+          <t>A-95b24a</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F112" t="n">

--- a/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
+++ b/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 14/09/2026 16:13</t>
+          <t>Gerado automaticamente em 14/09/2026 20:19</t>
         </is>
       </c>
     </row>
@@ -1482,27 +1482,27 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Company_115</t>
+          <t>Company_42</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>A-e61e98</t>
+          <t>A-7f8241</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1512,27 +1512,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Company_42</t>
+          <t>Company_115</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>A-7f8241</t>
+          <t>A-e61e98</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1632,22 +1632,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Company_195</t>
+          <t>Company_400</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>A-692f18</t>
+          <t>A-0f6450</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1662,22 +1662,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Company_400</t>
+          <t>Company_195</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>A-0f6450</t>
+          <t>A-692f18</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2772,27 +2772,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Company_324</t>
+          <t>Company_439</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A-6a7c9d</t>
+          <t>A-b11cd0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2802,27 +2802,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Company_439</t>
+          <t>Company_324</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A-b11cd0</t>
+          <t>A-6a7c9d</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -3462,27 +3462,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Company_185</t>
+          <t>Company_118</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A-139c3b</t>
+          <t>A-42e5e1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -3492,27 +3492,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Company_118</t>
+          <t>Company_185</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A-42e5e1</t>
+          <t>A-139c3b</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3582,27 +3582,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Company_200</t>
+          <t>Company_325</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>A-3be56b</t>
+          <t>A-cbd1a3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -3612,27 +3612,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Company_325</t>
+          <t>Company_200</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A-cbd1a3</t>
+          <t>A-3be56b</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3852,27 +3852,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Company_429</t>
+          <t>Company_357</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A-7641d3</t>
+          <t>A-1f559b</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3882,27 +3882,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Company_357</t>
+          <t>Company_429</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A-1f559b</t>
+          <t>A-7641d3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3912,17 +3912,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Company_59</t>
+          <t>Company_196</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A-9ee962</t>
+          <t>A-13466a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3942,17 +3942,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Company_196</t>
+          <t>Company_59</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A-13466a</t>
+          <t>A-9ee962</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -4122,27 +4122,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Company_149</t>
+          <t>Company_103</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A-eafc6e</t>
+          <t>A-69fad4</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4152,27 +4152,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Company_427</t>
+          <t>Company_144</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A-1d5444</t>
+          <t>A-3932db</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4182,12 +4182,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Company_126</t>
+          <t>Company_292</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A-1ac5e0</t>
+          <t>A-b07b56</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4212,22 +4212,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Company_8</t>
+          <t>Company_117</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A-7dacce</t>
+          <t>A-95b24a</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4242,17 +4242,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Company_79</t>
+          <t>Company_149</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A-9208f0</t>
+          <t>A-eafc6e</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4272,27 +4272,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Company_292</t>
+          <t>Company_233</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A-b07b56</t>
+          <t>A-ab438f</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4302,17 +4302,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Company_256</t>
+          <t>Company_427</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A-3ce5b8</t>
+          <t>A-1d5444</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4332,27 +4332,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Company_269</t>
+          <t>Company_256</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A-b07346</t>
+          <t>A-3ce5b8</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4362,22 +4362,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Company_417</t>
+          <t>Company_126</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A-659280</t>
+          <t>A-1ac5e0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4422,27 +4422,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Company_103</t>
+          <t>Company_79</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A-69fad4</t>
+          <t>A-9208f0</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4452,27 +4452,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Company_144</t>
+          <t>Company_8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A-3932db</t>
+          <t>A-7dacce</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -4482,12 +4482,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Company_117</t>
+          <t>Company_417</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A-95b24a</t>
+          <t>A-659280</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4512,27 +4512,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Company_233</t>
+          <t>Company_269</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A-ab438f</t>
+          <t>A-b07346</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F113" t="n">

--- a/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
+++ b/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 14/09/2026 20:19</t>
+          <t>Gerado automaticamente em 14/09/2026 20:34</t>
         </is>
       </c>
     </row>
@@ -1782,27 +1782,27 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Company_165</t>
+          <t>Company_415</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>A-ff79f2</t>
+          <t>A-1e50e0</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -1812,27 +1812,27 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Company_415</t>
+          <t>Company_165</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>A-1e50e0</t>
+          <t>A-ff79f2</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1872,27 +1872,27 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Company_18</t>
+          <t>Company_312</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>A-c4ea60</t>
+          <t>A-89ee83</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -1902,27 +1902,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Company_312</t>
+          <t>Company_18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A-89ee83</t>
+          <t>A-c4ea60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2202,27 +2202,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Company_32</t>
+          <t>Company_264</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A-08e34e</t>
+          <t>A-0baac2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2232,27 +2232,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Company_264</t>
+          <t>Company_32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A-0baac2</t>
+          <t>A-08e34e</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2292,27 +2292,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Company_463</t>
+          <t>Company_96</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A-798a3f</t>
+          <t>A-8b25f2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2322,27 +2322,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Company_96</t>
+          <t>Company_463</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A-8b25f2</t>
+          <t>A-798a3f</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2472,27 +2472,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Company_221</t>
+          <t>Company_110</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A-d922bf</t>
+          <t>A-425e76</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2502,27 +2502,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Company_110</t>
+          <t>Company_221</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A-425e76</t>
+          <t>A-d922bf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2772,12 +2772,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Company_439</t>
+          <t>Company_152</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A-b11cd0</t>
+          <t>A-439b2f</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2802,27 +2802,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Company_324</t>
+          <t>Company_439</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A-6a7c9d</t>
+          <t>A-b11cd0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2832,17 +2832,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Company_152</t>
+          <t>Company_324</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A-439b2f</t>
+          <t>A-6a7c9d</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3012,17 +3012,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Company_1</t>
+          <t>Company_10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A-43a9e3</t>
+          <t>A-592832</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3042,17 +3042,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Company_10</t>
+          <t>Company_1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A-592832</t>
+          <t>A-43a9e3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3462,27 +3462,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Company_118</t>
+          <t>Company_185</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A-42e5e1</t>
+          <t>A-139c3b</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -3492,27 +3492,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Company_185</t>
+          <t>Company_118</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A-139c3b</t>
+          <t>A-42e5e1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3912,17 +3912,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Company_196</t>
+          <t>Company_59</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A-13466a</t>
+          <t>A-9ee962</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3942,17 +3942,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Company_59</t>
+          <t>Company_196</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A-9ee962</t>
+          <t>A-13466a</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3972,22 +3972,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Company_280</t>
+          <t>Company_396</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A-443b7c</t>
+          <t>A-69b156</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4002,22 +4002,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Company_396</t>
+          <t>Company_280</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A-69b156</t>
+          <t>A-443b7c</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4122,22 +4122,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Company_103</t>
+          <t>Company_233</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A-69fad4</t>
+          <t>A-ab438f</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4152,27 +4152,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Company_144</t>
+          <t>Company_421</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A-3932db</t>
+          <t>A-d535f6</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4182,17 +4182,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Company_292</t>
+          <t>Company_144</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A-b07b56</t>
+          <t>A-3932db</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -4212,17 +4212,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Company_117</t>
+          <t>Company_269</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A-95b24a</t>
+          <t>A-b07346</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4242,12 +4242,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Company_149</t>
+          <t>Company_126</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A-eafc6e</t>
+          <t>A-1ac5e0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4272,17 +4272,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Company_233</t>
+          <t>Company_417</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A-ab438f</t>
+          <t>A-659280</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4302,27 +4302,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Company_427</t>
+          <t>Company_79</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A-1d5444</t>
+          <t>A-9208f0</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4332,27 +4332,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Company_256</t>
+          <t>Company_8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A-3ce5b8</t>
+          <t>A-7dacce</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4362,12 +4362,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Company_126</t>
+          <t>Company_149</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A-1ac5e0</t>
+          <t>A-eafc6e</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4392,27 +4392,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Company_421</t>
+          <t>Company_117</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A-d535f6</t>
+          <t>A-95b24a</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4422,27 +4422,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Company_79</t>
+          <t>Company_427</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A-9208f0</t>
+          <t>A-1d5444</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4452,22 +4452,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Company_8</t>
+          <t>Company_292</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A-7dacce</t>
+          <t>A-b07b56</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4482,12 +4482,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Company_417</t>
+          <t>Company_103</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A-659280</t>
+          <t>A-69fad4</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4512,27 +4512,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Company_269</t>
+          <t>Company_256</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A-b07346</t>
+          <t>A-3ce5b8</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F113" t="n">

--- a/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
+++ b/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo Executivo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Teste CEO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Contas em Risco (MRR)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Segmentação de Risco" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dados Brutos — Contas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo Executivo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste CEO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas em Risco (MRR)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segmentação de Risco" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados Brutos — Contas" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 14/09/2026 20:34</t>
+          <t>Gerado automaticamente em 14/09/2026 20:57</t>
         </is>
       </c>
     </row>
@@ -1782,27 +1782,27 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Company_415</t>
+          <t>Company_165</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>A-1e50e0</t>
+          <t>A-ff79f2</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -1812,27 +1812,27 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Company_165</t>
+          <t>Company_466</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>A-ff79f2</t>
+          <t>A-6f50ae</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1842,17 +1842,17 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Company_466</t>
+          <t>Company_415</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>A-6f50ae</t>
+          <t>A-1e50e0</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
@@ -1872,27 +1872,27 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Company_312</t>
+          <t>Company_18</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>A-89ee83</t>
+          <t>A-c4ea60</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -1902,27 +1902,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Company_18</t>
+          <t>Company_312</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A-c4ea60</t>
+          <t>A-89ee83</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1932,27 +1932,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Company_22</t>
+          <t>Company_288</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A-4e44e8</t>
+          <t>A-bcf87c</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1962,27 +1962,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Company_288</t>
+          <t>Company_22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A-bcf87c</t>
+          <t>A-4e44e8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -2292,27 +2292,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Company_96</t>
+          <t>Company_463</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A-8b25f2</t>
+          <t>A-798a3f</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -2322,27 +2322,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Company_463</t>
+          <t>Company_96</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A-798a3f</t>
+          <t>A-8b25f2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -2532,27 +2532,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Company_55</t>
+          <t>Company_327</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>A-4c38bc</t>
+          <t>A-600734</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2562,27 +2562,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Company_327</t>
+          <t>Company_55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>A-600734</t>
+          <t>A-4c38bc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2772,12 +2772,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Company_152</t>
+          <t>Company_439</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A-439b2f</t>
+          <t>A-b11cd0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2802,12 +2802,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Company_439</t>
+          <t>Company_152</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A-b11cd0</t>
+          <t>A-439b2f</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3012,17 +3012,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Company_10</t>
+          <t>Company_1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A-592832</t>
+          <t>A-43a9e3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3042,17 +3042,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Company_1</t>
+          <t>Company_10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A-43a9e3</t>
+          <t>A-592832</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3342,27 +3342,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Company_229</t>
+          <t>Company_369</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A-4ae22a</t>
+          <t>A-40de06</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -3372,27 +3372,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Company_369</t>
+          <t>Company_229</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A-40de06</t>
+          <t>A-4ae22a</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3462,27 +3462,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Company_185</t>
+          <t>Company_118</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A-139c3b</t>
+          <t>A-42e5e1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -3492,27 +3492,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Company_118</t>
+          <t>Company_185</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A-42e5e1</t>
+          <t>A-139c3b</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3852,27 +3852,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Company_357</t>
+          <t>Company_429</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A-1f559b</t>
+          <t>A-7641d3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3882,27 +3882,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Company_429</t>
+          <t>Company_357</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>A-7641d3</t>
+          <t>A-1f559b</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3972,22 +3972,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Company_396</t>
+          <t>Company_280</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A-69b156</t>
+          <t>A-443b7c</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4002,22 +4002,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Company_280</t>
+          <t>Company_396</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A-443b7c</t>
+          <t>A-69b156</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4122,12 +4122,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Company_233</t>
+          <t>Company_427</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A-ab438f</t>
+          <t>A-1d5444</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4152,27 +4152,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Company_421</t>
+          <t>Company_144</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A-d535f6</t>
+          <t>A-3932db</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4182,27 +4182,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Company_144</t>
+          <t>Company_256</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A-3932db</t>
+          <t>A-3ce5b8</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -4212,27 +4212,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Company_269</t>
+          <t>Company_421</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A-b07346</t>
+          <t>A-d535f6</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4242,27 +4242,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Company_126</t>
+          <t>Company_233</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A-1ac5e0</t>
+          <t>A-ab438f</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4272,27 +4272,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Company_417</t>
+          <t>Company_269</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A-659280</t>
+          <t>A-b07346</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4332,22 +4332,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Company_8</t>
+          <t>Company_126</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A-7dacce</t>
+          <t>A-1ac5e0</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4362,27 +4362,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Company_149</t>
+          <t>Company_8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A-eafc6e</t>
+          <t>A-7dacce</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4392,17 +4392,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Company_117</t>
+          <t>Company_292</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A-95b24a</t>
+          <t>A-b07b56</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4422,17 +4422,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Company_427</t>
+          <t>Company_103</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A-1d5444</t>
+          <t>A-69fad4</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4452,17 +4452,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Company_292</t>
+          <t>Company_117</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A-b07b56</t>
+          <t>A-95b24a</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4482,27 +4482,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Company_103</t>
+          <t>Company_149</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A-69fad4</t>
+          <t>A-eafc6e</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4512,12 +4512,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Company_256</t>
+          <t>Company_417</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A-3ce5b8</t>
+          <t>A-659280</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F113" t="n">

--- a/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
+++ b/submissions/alexandre-denofrio/RavenStack_Diagnostico_Churn.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gerado automaticamente em 14/09/2026 20:57</t>
+          <t>Gerado automaticamente em 14/09/2026 21:33</t>
         </is>
       </c>
     </row>
@@ -1482,27 +1482,27 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Company_42</t>
+          <t>Company_115</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>A-7f8241</t>
+          <t>A-e61e98</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1512,27 +1512,27 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Company_115</t>
+          <t>Company_42</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>A-e61e98</t>
+          <t>A-7f8241</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1782,27 +1782,27 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Company_165</t>
+          <t>Company_466</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>A-ff79f2</t>
+          <t>A-6f50ae</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -1812,27 +1812,27 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Company_466</t>
+          <t>Company_165</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>A-6f50ae</t>
+          <t>A-ff79f2</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -2052,17 +2052,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Company_436</t>
+          <t>Company_187</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A-34ea2f</t>
+          <t>A-7a0d69</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2082,17 +2082,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Company_187</t>
+          <t>Company_436</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A-7a0d69</t>
+          <t>A-34ea2f</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2202,27 +2202,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Company_264</t>
+          <t>Company_32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A-0baac2</t>
+          <t>A-08e34e</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2232,27 +2232,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Company_32</t>
+          <t>Company_264</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A-08e34e</t>
+          <t>A-0baac2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2772,27 +2772,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Company_439</t>
+          <t>Company_324</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>A-b11cd0</t>
+          <t>A-6a7c9d</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2802,12 +2802,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Company_152</t>
+          <t>Company_439</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>A-439b2f</t>
+          <t>A-b11cd0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2832,17 +2832,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Company_324</t>
+          <t>Company_152</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>A-6a7c9d</t>
+          <t>A-439b2f</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3012,17 +3012,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Company_1</t>
+          <t>Company_10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>A-43a9e3</t>
+          <t>A-592832</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -3042,17 +3042,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Company_10</t>
+          <t>Company_1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A-592832</t>
+          <t>A-43a9e3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -3342,27 +3342,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Company_369</t>
+          <t>Company_229</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>A-40de06</t>
+          <t>A-4ae22a</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -3372,27 +3372,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Company_229</t>
+          <t>Company_369</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>A-4ae22a</t>
+          <t>A-40de06</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3462,27 +3462,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Company_118</t>
+          <t>Company_185</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>A-42e5e1</t>
+          <t>A-139c3b</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -3492,27 +3492,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Company_185</t>
+          <t>Company_118</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>A-139c3b</t>
+          <t>A-42e5e1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3912,17 +3912,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Company_59</t>
+          <t>Company_196</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A-9ee962</t>
+          <t>A-13466a</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3942,17 +3942,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Company_196</t>
+          <t>Company_59</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A-13466a</t>
+          <t>A-9ee962</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3972,22 +3972,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Company_280</t>
+          <t>Company_396</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A-443b7c</t>
+          <t>A-69b156</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4002,22 +4002,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Company_396</t>
+          <t>Company_280</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A-69b156</t>
+          <t>A-443b7c</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4122,27 +4122,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Company_427</t>
+          <t>Company_79</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A-1d5444</t>
+          <t>A-9208f0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>EdTech</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -4152,17 +4152,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Company_144</t>
+          <t>Company_117</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>A-3932db</t>
+          <t>A-95b24a</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -4182,17 +4182,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Company_256</t>
+          <t>Company_421</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A-3ce5b8</t>
+          <t>A-d535f6</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -4212,27 +4212,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Company_421</t>
+          <t>Company_144</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A-d535f6</t>
+          <t>A-3932db</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -4242,27 +4242,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Company_233</t>
+          <t>Company_269</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A-ab438f</t>
+          <t>A-b07346</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>HealthTech</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -4272,17 +4272,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Company_269</t>
+          <t>Company_292</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A-b07346</t>
+          <t>A-b07b56</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HealthTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4302,27 +4302,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Company_79</t>
+          <t>Company_103</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A-9208f0</t>
+          <t>A-69fad4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>EdTech</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4332,22 +4332,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Company_126</t>
+          <t>Company_417</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A-1ac5e0</t>
+          <t>A-659280</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4362,27 +4362,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Company_8</t>
+          <t>Company_256</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>A-7dacce</t>
+          <t>A-3ce5b8</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cybersecurity</t>
+          <t>FinTech</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4392,27 +4392,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Company_292</t>
+          <t>Company_233</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>A-b07b56</t>
+          <t>A-ab438f</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DevTools</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>ads</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4422,27 +4422,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Company_103</t>
+          <t>Company_8</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>A-69fad4</t>
+          <t>A-7dacce</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Enterprise</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ads</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4452,17 +4452,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Company_117</t>
+          <t>Company_149</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>A-95b24a</t>
+          <t>A-eafc6e</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>DevTools</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -4482,12 +4482,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Company_149</t>
+          <t>Company_126</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>A-eafc6e</t>
+          <t>A-1ac5e0</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>event</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4512,27 +4512,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Company_417</t>
+          <t>Company_427</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>A-659280</t>
+          <t>A-1d5444</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FinTech</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Enterprise</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="F113" t="n">
